--- a/Data/EXCEL/Transfer/salemon/202208/6835-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6835-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{773C1D2D-5771-4514-828F-C8AEC9EB0DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FFA1C00-1661-48B5-B2EF-A615CF30DA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6835-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -261,9 +261,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
-      <name val="新細明體"/>
-      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,25 +1226,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="8" width="8.625" customWidth="1"/>
-    <col min="9" max="9" width="10.125" customWidth="1"/>
-    <col min="10" max="10" width="9.625" customWidth="1"/>
-    <col min="11" max="11" width="10.125" customWidth="1"/>
-    <col min="12" max="12" width="9.625" customWidth="1"/>
-    <col min="13" max="13" width="8.625" customWidth="1"/>
-    <col min="14" max="14" width="10.125" customWidth="1"/>
-    <col min="15" max="15" width="9.625" customWidth="1"/>
-    <col min="16" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="14.125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1270,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1302,7 +1309,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1345,7 +1352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1384,851 +1391,904 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
+        <v>44774</v>
+      </c>
+      <c r="B5" s="7">
+        <v>49</v>
+      </c>
+      <c r="C5" s="7">
+        <v>50.7</v>
+      </c>
+      <c r="D5" s="7">
+        <v>53</v>
+      </c>
+      <c r="E5" s="7">
+        <v>48</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="G5" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="H5" s="9">
+        <v>2.39</v>
+      </c>
+      <c r="I5" s="10">
+        <v>-7.51</v>
+      </c>
+      <c r="J5" s="8">
+        <v>15.1</v>
+      </c>
+      <c r="K5" s="9">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="L5" s="8">
+        <v>5.05</v>
+      </c>
+      <c r="M5" s="9">
+        <v>2.39</v>
+      </c>
+      <c r="N5" s="10">
+        <v>-7.51</v>
+      </c>
+      <c r="O5" s="8">
+        <v>15.1</v>
+      </c>
+      <c r="P5" s="9">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>44743</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B6" s="7">
         <v>51.5</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C6" s="7">
         <v>49</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D6" s="7">
         <v>52.2</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E6" s="7">
         <v>48.3</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F6" s="10">
         <v>-2.5</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G6" s="10">
         <v>-4.8499999999999996</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H6" s="9">
         <v>2.58</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I6" s="10">
         <v>-0.52</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J6" s="8">
         <v>9.9700000000000006</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K6" s="9">
         <v>16.47</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L6" s="8">
         <v>3.73</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M6" s="9">
         <v>2.58</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N6" s="10">
         <v>-0.52</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O6" s="8">
         <v>9.9700000000000006</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P6" s="9">
         <v>16.47</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q6" s="8">
         <v>3.73</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
-      <c r="A6" s="6">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>44713</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B7" s="7">
         <v>51.2</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C7" s="7">
         <v>51.5</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D7" s="7">
         <v>52.1</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E7" s="7">
         <v>47.1</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F7" s="8">
         <v>0.3</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G7" s="8">
         <v>0.59</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H7" s="9">
         <v>2.6</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I7" s="10">
         <v>-12.9</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J7" s="8">
         <v>16.899999999999999</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K7" s="9">
         <v>13.88</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L7" s="8">
         <v>2.65</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M7" s="9">
         <v>2.6</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N7" s="10">
         <v>-12.9</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O7" s="8">
         <v>16.899999999999999</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P7" s="9">
         <v>13.88</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q7" s="8">
         <v>2.65</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
-      <c r="A7" s="6">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>44682</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B8" s="7">
         <v>51.9</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C8" s="7">
         <v>51.2</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D8" s="7">
         <v>52</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E8" s="7">
         <v>50</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F8" s="10">
         <v>-0.7</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G8" s="10">
         <v>-1.35</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H8" s="9">
         <v>2.98</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I8" s="8">
         <v>114.8</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J8" s="8">
         <v>29.4</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K8" s="9">
         <v>11.29</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L8" s="10">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M8" s="9">
         <v>2.98</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N8" s="8">
         <v>114.8</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O8" s="8">
         <v>29.4</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P8" s="9">
         <v>11.29</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q8" s="10">
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
-      <c r="A8" s="6">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>44652</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B9" s="7">
         <v>51.7</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C9" s="7">
         <v>51.9</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D9" s="7">
         <v>52.2</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E9" s="7">
         <v>50.8</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F9" s="8">
         <v>0.2</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G9" s="8">
         <v>0.39</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H9" s="9">
         <v>1.39</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I9" s="10">
         <v>-47.9</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J9" s="10">
         <v>-40.1</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K9" s="9">
         <v>8.31</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L9" s="10">
         <v>-7.7</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M9" s="9">
         <v>1.39</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N9" s="10">
         <v>-47.9</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O9" s="10">
         <v>-40.1</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P9" s="9">
         <v>8.31</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q9" s="10">
         <v>-7.7</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
-      <c r="A9" s="6">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>44621</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B10" s="7">
         <v>50.2</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C10" s="7">
         <v>51.7</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D10" s="7">
         <v>52.5</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E10" s="7">
         <v>48.3</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F10" s="8">
         <v>1.5</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G10" s="8">
         <v>2.99</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H10" s="9">
         <v>2.66</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I10" s="8">
         <v>56.8</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J10" s="8">
         <v>15.9</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K10" s="9">
         <v>6.92</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L10" s="8">
         <v>3.55</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M10" s="9">
         <v>2.66</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N10" s="8">
         <v>56.8</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O10" s="8">
         <v>15.9</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P10" s="9">
         <v>6.92</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q10" s="8">
         <v>3.55</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
-      <c r="A10" s="6">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>44593</v>
-      </c>
-      <c r="B10" s="7">
-        <v>49</v>
-      </c>
-      <c r="C10" s="7">
-        <v>50.2</v>
-      </c>
-      <c r="D10" s="7">
-        <v>50.8</v>
-      </c>
-      <c r="E10" s="7">
-        <v>47.2</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="G10" s="10">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="H10" s="9">
-        <v>1.7</v>
-      </c>
-      <c r="I10" s="8">
-        <v>-33.5</v>
-      </c>
-      <c r="J10" s="8">
-        <v>-2.33</v>
-      </c>
-      <c r="K10" s="9">
-        <v>4.25</v>
-      </c>
-      <c r="L10" s="8">
-        <v>-2.94</v>
-      </c>
-      <c r="M10" s="9">
-        <v>1.7</v>
-      </c>
-      <c r="N10" s="8">
-        <v>-33.5</v>
-      </c>
-      <c r="O10" s="8">
-        <v>-2.33</v>
-      </c>
-      <c r="P10" s="9">
-        <v>4.25</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
-      <c r="A11" s="6">
-        <v>44562</v>
       </c>
       <c r="B11" s="7">
         <v>49</v>
       </c>
       <c r="C11" s="7">
+        <v>50.2</v>
+      </c>
+      <c r="D11" s="7">
+        <v>50.8</v>
+      </c>
+      <c r="E11" s="7">
+        <v>47.2</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="G11" s="8">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="H11" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="I11" s="10">
+        <v>-33.5</v>
+      </c>
+      <c r="J11" s="10">
+        <v>-2.33</v>
+      </c>
+      <c r="K11" s="9">
+        <v>4.25</v>
+      </c>
+      <c r="L11" s="10">
+        <v>-2.94</v>
+      </c>
+      <c r="M11" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="N11" s="10">
+        <v>-33.5</v>
+      </c>
+      <c r="O11" s="10">
+        <v>-2.33</v>
+      </c>
+      <c r="P11" s="9">
+        <v>4.25</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>44562</v>
+      </c>
+      <c r="B12" s="7">
         <v>49</v>
-      </c>
-      <c r="D11" s="7">
-        <v>49.2</v>
-      </c>
-      <c r="E11" s="7">
-        <v>47</v>
-      </c>
-      <c r="F11" s="9">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="I11" s="8">
-        <v>-1.88</v>
-      </c>
-      <c r="J11" s="8">
-        <v>-3.35</v>
-      </c>
-      <c r="K11" s="9">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="L11" s="8">
-        <v>-3.35</v>
-      </c>
-      <c r="M11" s="9">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="N11" s="8">
-        <v>-1.88</v>
-      </c>
-      <c r="O11" s="8">
-        <v>-3.35</v>
-      </c>
-      <c r="P11" s="9">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>-3.35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
-      <c r="A12" s="6">
-        <v>44531</v>
-      </c>
-      <c r="B12" s="7">
-        <v>49.5</v>
       </c>
       <c r="C12" s="7">
         <v>49</v>
       </c>
       <c r="D12" s="7">
+        <v>49.2</v>
+      </c>
+      <c r="E12" s="7">
+        <v>47</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="I12" s="10">
+        <v>-1.88</v>
+      </c>
+      <c r="J12" s="10">
+        <v>-3.35</v>
+      </c>
+      <c r="K12" s="9">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="L12" s="10">
+        <v>-3.35</v>
+      </c>
+      <c r="M12" s="9">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="N12" s="10">
+        <v>-1.88</v>
+      </c>
+      <c r="O12" s="10">
+        <v>-3.35</v>
+      </c>
+      <c r="P12" s="9">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>-3.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>44531</v>
+      </c>
+      <c r="B13" s="7">
+        <v>49.5</v>
+      </c>
+      <c r="C13" s="7">
+        <v>49</v>
+      </c>
+      <c r="D13" s="7">
         <v>50.5</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E13" s="7">
         <v>45.5</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F13" s="10">
         <v>-0.5</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G13" s="10">
         <v>-1.01</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H13" s="9">
         <v>2.6</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I13" s="8">
         <v>4.47</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J13" s="8">
         <v>7.62</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K13" s="9">
         <v>27.88</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L13" s="8">
         <v>12.3</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M13" s="9">
         <v>2.6</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N13" s="8">
         <v>4.47</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O13" s="8">
         <v>7.62</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P13" s="9">
         <v>27.88</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="Q13" s="8">
         <v>12.3</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
-      <c r="A13" s="6">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>44501</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B14" s="7">
         <v>46.2</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C14" s="7">
         <v>49.5</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D14" s="7">
         <v>51.5</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E14" s="7">
         <v>45.75</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F14" s="8">
         <v>3.3</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G14" s="8">
         <v>7.14</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H14" s="9">
         <v>2.4900000000000002</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I14" s="10">
         <v>-0.77</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J14" s="8">
         <v>25.8</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K14" s="9">
         <v>25.28</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L14" s="8">
         <v>12.8</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M14" s="9">
         <v>2.4900000000000002</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N14" s="10">
         <v>-0.77</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O14" s="8">
         <v>25.8</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P14" s="9">
         <v>25.28</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="Q14" s="8">
         <v>12.8</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
-      <c r="A14" s="6">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>44470</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B15" s="7">
         <v>47</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C15" s="7">
         <v>46.2</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D15" s="7">
         <v>47.15</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E15" s="7">
         <v>44.1</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F15" s="10">
         <v>-0.8</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G15" s="10">
         <v>-1.7</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H15" s="9">
         <v>2.5099999999999998</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I15" s="8">
         <v>7.8</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J15" s="8">
         <v>9.99</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K15" s="9">
         <v>22.79</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L15" s="8">
         <v>11.6</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M15" s="9">
         <v>2.5099999999999998</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N15" s="8">
         <v>7.8</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O15" s="8">
         <v>9.99</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P15" s="9">
         <v>22.79</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q15" s="8">
         <v>11.6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
-      <c r="A15" s="6">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
         <v>44440</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B16" s="7">
         <v>45.85</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C16" s="7">
         <v>47</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D16" s="7">
         <v>51.2</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E16" s="7">
         <v>44.7</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F16" s="8">
         <v>1.1499999999999999</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G16" s="8">
         <v>2.5099999999999998</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H16" s="9">
         <v>2.33</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I16" s="8">
         <v>12.2</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J16" s="8">
         <v>18</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K16" s="9">
         <v>20.28</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L16" s="8">
         <v>11.8</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M16" s="9">
         <v>2.33</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N16" s="8">
         <v>12.2</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O16" s="8">
         <v>18</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P16" s="9">
         <v>20.28</v>
       </c>
-      <c r="Q15" s="10">
+      <c r="Q16" s="8">
         <v>11.8</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
-      <c r="A16" s="6">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>44409</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B17" s="7">
         <v>62</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C17" s="7">
         <v>45.85</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D17" s="7">
         <v>81</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E17" s="7">
         <v>43.35</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F17" s="10">
         <v>-16.149999999999999</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G17" s="10">
         <v>-26.05</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H17" s="9">
         <v>2.08</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I17" s="10">
         <v>-11.6</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J17" s="10">
         <v>-17.7</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K17" s="9">
         <v>17.95</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L17" s="8">
         <v>11</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M17" s="9">
         <v>2.08</v>
       </c>
-      <c r="N16" s="8">
+      <c r="N17" s="10">
         <v>-11.6</v>
       </c>
-      <c r="O16" s="8">
+      <c r="O17" s="10">
         <v>-17.7</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P17" s="9">
         <v>17.95</v>
       </c>
-      <c r="Q16" s="10">
+      <c r="Q17" s="8">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
-      <c r="A17" s="6">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>44378</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="9">
+      <c r="B18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="9">
         <v>2.35</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I18" s="8">
         <v>5.74</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J18" s="10">
         <v>-4.96</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K18" s="9">
         <v>15.87</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L18" s="8">
         <v>16.3</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M18" s="9">
         <v>2.35</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N18" s="8">
         <v>5.74</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O18" s="10">
         <v>-4.96</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P18" s="9">
         <v>15.87</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q18" s="8">
         <v>16.3</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
-      <c r="A18" s="6">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>44348</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="9">
+      <c r="B19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="9">
         <v>2.2200000000000002</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I19" s="10">
         <v>-3.62</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J19" s="10">
         <v>-2.71</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K19" s="9">
         <v>13.52</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L19" s="8">
         <v>21</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M19" s="9">
         <v>2.2200000000000002</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N19" s="10">
         <v>-3.62</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O19" s="10">
         <v>-2.71</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P19" s="9">
         <v>13.52</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="Q19" s="8">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
-      <c r="A19" s="6">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
         <v>44317</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="9">
+      <c r="B20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I20" s="10">
         <v>-0.63</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J20" s="8">
         <v>0.31</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K20" s="9">
         <v>11.3</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L20" s="8">
         <v>27.1</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M20" s="9">
         <v>2.2999999999999998</v>
       </c>
-      <c r="N19" s="8">
+      <c r="N20" s="10">
         <v>-0.63</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O20" s="8">
         <v>0.31</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P20" s="9">
         <v>11.3</v>
       </c>
-      <c r="Q19" s="10">
+      <c r="Q20" s="8">
         <v>27.1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
-      <c r="A20" s="6">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
         <v>44287</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="9">
+      <c r="B21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="9">
         <v>2.3199999999999998</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="8">
+      <c r="I21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="10">
         <v>-1.55</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K21" s="9">
         <v>9</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L21" s="8">
         <v>36.4</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M21" s="9">
         <v>2.3199999999999998</v>
       </c>
-      <c r="N20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O20" s="8">
+      <c r="N21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" s="10">
         <v>-1.55</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P21" s="9">
         <v>9</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="Q21" s="8">
         <v>36.4</v>
       </c>
     </row>
@@ -2247,7 +2307,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>